--- a/data/test/nuclear_safety_test.xlsx
+++ b/data/test/nuclear_safety_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yana.vyklyuk/Documents/GitHub/open-data-ai-analytics/data/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9E7029-6D37-0B4D-BCB6-E64C35BBEBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F28CEE-993D-A444-943C-CCC2BABDDCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4540" yWindow="600" windowWidth="26180" windowHeight="17140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Аркуш 1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>year</t>
   </si>
@@ -738,15 +738,54 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="B5" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>16</v>
+      </c>
+      <c r="D5" s="12">
+        <v>80</v>
+      </c>
+      <c r="E5" s="12">
+        <v>0.12</v>
+      </c>
+      <c r="F5" s="12">
+        <v>234</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="12">
+        <v>637</v>
+      </c>
+      <c r="I5" s="12">
+        <v>0.03</v>
+      </c>
+      <c r="J5" s="12">
+        <v>230</v>
+      </c>
+      <c r="K5" s="12">
+        <v>342</v>
+      </c>
+      <c r="L5" s="12">
+        <v>3813</v>
+      </c>
+      <c r="M5" s="12">
+        <v>3062</v>
+      </c>
+      <c r="N5" s="11">
+        <v>825352</v>
+      </c>
+      <c r="O5" s="13">
+        <v>0.72</v>
+      </c>
+      <c r="P5" s="14">
+        <v>1.05</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -757,46 +796,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="12">
-        <v>131</v>
-      </c>
-      <c r="E6" s="12">
-        <v>0.22</v>
-      </c>
-      <c r="F6" s="12">
-        <v>19</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="12">
-        <v>297</v>
-      </c>
-      <c r="I6" s="12">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="J6" s="12">
-        <v>178</v>
-      </c>
-      <c r="K6" s="12">
-        <v>368</v>
-      </c>
-      <c r="L6" s="12">
-        <v>5813</v>
-      </c>
-      <c r="M6" s="12">
-        <v>1246</v>
-      </c>
-      <c r="N6" s="11">
-        <v>3809200</v>
-      </c>
-      <c r="O6" s="13">
-        <v>0.41</v>
-      </c>
-      <c r="P6" s="14">
-        <v>0.31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
@@ -807,46 +807,46 @@
         <v>3</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D7" s="12">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="E7" s="12">
-        <v>0.08</v>
+        <v>0.22</v>
       </c>
       <c r="F7" s="12">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="12">
-        <v>33</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>17</v>
+        <v>297</v>
+      </c>
+      <c r="I7" s="12">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="J7" s="12">
-        <v>44</v>
+        <v>178</v>
       </c>
       <c r="K7" s="12">
-        <v>21</v>
+        <v>368</v>
       </c>
       <c r="L7" s="12">
-        <v>1730</v>
+        <v>5813</v>
       </c>
       <c r="M7" s="12">
-        <v>39</v>
+        <v>1246</v>
       </c>
       <c r="N7" s="11">
-        <v>65840</v>
+        <v>3809200</v>
       </c>
       <c r="O7" s="13">
-        <v>0.85</v>
+        <v>0.41</v>
       </c>
       <c r="P7" s="14">
-        <v>0.19800000000000001</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -854,10 +854,49 @@
         <v>2024</v>
       </c>
       <c r="B8" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="D8" s="12">
+        <v>33</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0.08</v>
+      </c>
+      <c r="F8" s="12">
+        <v>39</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="12">
+        <v>33</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="12">
+        <v>44</v>
+      </c>
+      <c r="K8" s="12">
+        <v>21</v>
+      </c>
+      <c r="L8" s="12">
+        <v>1730</v>
+      </c>
+      <c r="M8" s="12">
+        <v>39</v>
+      </c>
+      <c r="N8" s="11">
+        <v>65840</v>
+      </c>
+      <c r="O8" s="13">
+        <v>0.85</v>
+      </c>
+      <c r="P8" s="14">
+        <v>0.19800000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
@@ -868,57 +907,57 @@
         <v>4</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="12">
-        <v>132</v>
-      </c>
-      <c r="E9" s="12">
-        <v>0.22</v>
-      </c>
-      <c r="F9" s="12">
         <v>16</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="12">
-        <v>239</v>
-      </c>
-      <c r="I9" s="12">
-        <v>0.06</v>
-      </c>
-      <c r="J9" s="12">
-        <v>175</v>
-      </c>
-      <c r="K9" s="12">
-        <v>126</v>
-      </c>
-      <c r="L9" s="12">
-        <v>3479</v>
-      </c>
-      <c r="M9" s="12">
-        <v>905</v>
-      </c>
-      <c r="N9" s="11">
-        <v>2808750</v>
-      </c>
-      <c r="O9" s="13">
-        <v>0.42</v>
-      </c>
-      <c r="P9" s="14">
-        <v>0.45</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B10" s="11">
         <v>4</v>
       </c>
       <c r="C10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="12">
+        <v>132</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0.22</v>
+      </c>
+      <c r="F10" s="12">
         <v>16</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="12">
+        <v>239</v>
+      </c>
+      <c r="I10" s="12">
+        <v>0.06</v>
+      </c>
+      <c r="J10" s="12">
+        <v>175</v>
+      </c>
+      <c r="K10" s="12">
+        <v>126</v>
+      </c>
+      <c r="L10" s="12">
+        <v>3479</v>
+      </c>
+      <c r="M10" s="12">
+        <v>905</v>
+      </c>
+      <c r="N10" s="11">
+        <v>2808750</v>
+      </c>
+      <c r="O10" s="13">
+        <v>0.42</v>
+      </c>
+      <c r="P10" s="14">
+        <v>0.45</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">

--- a/data/test/nuclear_safety_test.xlsx
+++ b/data/test/nuclear_safety_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yana.vyklyuk/Documents/GitHub/open-data-ai-analytics/data/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F28CEE-993D-A444-943C-CCC2BABDDCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34B2CB2-0083-7D47-93E6-47897B21115D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4540" yWindow="600" windowWidth="26180" windowHeight="17140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Аркуш 1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="24">
   <si>
     <t>year</t>
   </si>
@@ -518,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="6" bestFit="1" customWidth="1"/>
@@ -788,225 +788,822 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B6" s="11">
-        <v>3</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="12">
+        <v>31</v>
+      </c>
+      <c r="E6" s="12">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F6" s="12">
+        <v>84</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="12">
+        <v>32</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="12">
+        <v>35</v>
+      </c>
+      <c r="K6" s="12">
+        <v>23</v>
+      </c>
+      <c r="L6" s="12">
+        <v>540</v>
+      </c>
+      <c r="N6" s="11">
+        <v>23812</v>
+      </c>
+      <c r="O6" s="13">
+        <v>0.11</v>
+      </c>
+      <c r="P6" s="14">
+        <v>0.03</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B7" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D7" s="12">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E7" s="12">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="F7" s="12">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="12">
-        <v>297</v>
+        <v>500</v>
       </c>
       <c r="I7" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="J7" s="12">
-        <v>178</v>
+        <v>1011</v>
       </c>
       <c r="K7" s="12">
-        <v>368</v>
+        <v>313</v>
       </c>
       <c r="L7" s="12">
-        <v>5813</v>
+        <v>3581</v>
       </c>
       <c r="M7" s="12">
-        <v>1246</v>
+        <v>3421</v>
       </c>
       <c r="N7" s="11">
-        <v>3809200</v>
+        <v>833700</v>
       </c>
       <c r="O7" s="13">
-        <v>0.41</v>
+        <v>1.07</v>
       </c>
       <c r="P7" s="14">
-        <v>0.31</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B8" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D8" s="12">
-        <v>33</v>
+        <v>147</v>
       </c>
       <c r="E8" s="12">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="F8" s="12">
-        <v>39</v>
+        <v>176</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="12">
-        <v>33</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>17</v>
+        <v>256</v>
+      </c>
+      <c r="I8" s="12">
+        <v>0.06</v>
       </c>
       <c r="J8" s="12">
-        <v>44</v>
+        <v>621</v>
       </c>
       <c r="K8" s="12">
-        <v>21</v>
+        <v>583</v>
       </c>
       <c r="L8" s="12">
-        <v>1730</v>
+        <v>8654</v>
       </c>
       <c r="M8" s="12">
-        <v>39</v>
+        <v>1426</v>
       </c>
       <c r="N8" s="11">
-        <v>65840</v>
+        <v>3090500</v>
       </c>
       <c r="O8" s="13">
-        <v>0.85</v>
+        <v>0.63</v>
       </c>
       <c r="P8" s="14">
-        <v>0.19800000000000001</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B9" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>16</v>
+        <v>23</v>
+      </c>
+      <c r="D9" s="12">
+        <v>27</v>
+      </c>
+      <c r="E9" s="12">
+        <v>0.06</v>
+      </c>
+      <c r="F9" s="12">
+        <v>98</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="12">
+        <v>223</v>
+      </c>
+      <c r="I9" s="12">
+        <v>0.03</v>
+      </c>
+      <c r="J9" s="12">
+        <v>97</v>
+      </c>
+      <c r="K9" s="12">
+        <v>269</v>
+      </c>
+      <c r="L9" s="12">
+        <v>653</v>
+      </c>
+      <c r="M9" s="12">
+        <v>649</v>
+      </c>
+      <c r="N9" s="11">
+        <v>25700</v>
+      </c>
+      <c r="O9" s="13">
+        <v>3.04</v>
+      </c>
+      <c r="P9" s="14">
+        <v>1.19</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B10" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D10" s="12">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="E10" s="12">
-        <v>0.22</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F10" s="12">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="12">
-        <v>239</v>
-      </c>
-      <c r="I10" s="12">
-        <v>0.06</v>
+        <v>36</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="J10" s="12">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="K10" s="12">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="L10" s="12">
-        <v>3479</v>
+        <v>987</v>
       </c>
       <c r="M10" s="12">
-        <v>905</v>
+        <v>76</v>
       </c>
       <c r="N10" s="11">
-        <v>2808750</v>
+        <v>64464</v>
       </c>
       <c r="O10" s="13">
-        <v>0.42</v>
+        <v>0.16</v>
       </c>
       <c r="P10" s="14">
-        <v>0.45</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
+        <v>2022</v>
+      </c>
+      <c r="B11" s="11">
+        <v>3</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="12">
+        <v>81</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0.11</v>
+      </c>
+      <c r="F11" s="12">
+        <v>64</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="12">
+        <v>450</v>
+      </c>
+      <c r="I11" s="12">
+        <v>0.06</v>
+      </c>
+      <c r="J11" s="12">
+        <v>202</v>
+      </c>
+      <c r="K11" s="12">
+        <v>163</v>
+      </c>
+      <c r="L11" s="12">
+        <v>2033</v>
+      </c>
+      <c r="M11" s="12">
+        <v>9000</v>
+      </c>
+      <c r="N11" s="11">
+        <v>601000</v>
+      </c>
+      <c r="O11" s="13">
+        <v>0.84</v>
+      </c>
+      <c r="P11" s="14">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
+        <v>2022</v>
+      </c>
+      <c r="B12" s="11">
+        <v>3</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="12">
+        <v>176</v>
+      </c>
+      <c r="E12" s="12">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F12" s="12">
+        <v>31</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="12">
+        <v>236</v>
+      </c>
+      <c r="I12" s="12">
+        <v>0.06</v>
+      </c>
+      <c r="J12" s="12">
+        <v>1046</v>
+      </c>
+      <c r="K12" s="12">
+        <v>201</v>
+      </c>
+      <c r="L12" s="12">
+        <v>9032</v>
+      </c>
+      <c r="M12" s="12">
+        <v>1555</v>
+      </c>
+      <c r="N12" s="11">
+        <v>3259600</v>
+      </c>
+      <c r="O12" s="13">
+        <v>0.59</v>
+      </c>
+      <c r="P12" s="14">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>2022</v>
+      </c>
+      <c r="B13" s="11">
+        <v>3</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="12">
+        <v>26</v>
+      </c>
+      <c r="E13" s="12">
+        <v>0.06</v>
+      </c>
+      <c r="F13" s="12">
+        <v>65</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="12">
+        <v>217</v>
+      </c>
+      <c r="I13" s="12">
+        <v>0.03</v>
+      </c>
+      <c r="J13" s="12">
+        <v>53</v>
+      </c>
+      <c r="K13" s="12">
+        <v>158</v>
+      </c>
+      <c r="L13" s="12">
+        <v>199</v>
+      </c>
+      <c r="M13" s="12">
+        <v>197</v>
+      </c>
+      <c r="N13" s="11">
+        <v>8000</v>
+      </c>
+      <c r="O13" s="13">
+        <v>2.98</v>
+      </c>
+      <c r="P13" s="14">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" s="6">
+        <v>2022</v>
+      </c>
+      <c r="B14" s="11">
+        <v>3</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="12">
+        <v>30</v>
+      </c>
+      <c r="E14" s="12">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F14" s="12">
+        <v>31</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="12">
+        <v>33</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="12">
+        <v>30</v>
+      </c>
+      <c r="K14" s="12">
+        <v>22</v>
+      </c>
+      <c r="L14" s="12">
+        <v>232</v>
+      </c>
+      <c r="M14" s="12">
+        <v>15</v>
+      </c>
+      <c r="N14" s="11">
+        <v>4716</v>
+      </c>
+      <c r="O14" s="13">
+        <v>0.12</v>
+      </c>
+      <c r="P14" s="14">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A15" s="6">
+        <v>2023</v>
+      </c>
+      <c r="B15" s="11">
+        <v>4</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="12">
+        <v>128</v>
+      </c>
+      <c r="E15" s="12">
+        <v>0.21</v>
+      </c>
+      <c r="F15" s="12">
+        <v>65</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="12">
+        <v>227</v>
+      </c>
+      <c r="I15" s="12">
+        <v>0.06</v>
+      </c>
+      <c r="J15" s="12">
+        <v>324</v>
+      </c>
+      <c r="K15" s="12">
+        <v>150</v>
+      </c>
+      <c r="L15" s="12">
+        <v>5999</v>
+      </c>
+      <c r="M15" s="12">
+        <v>552</v>
+      </c>
+      <c r="N15" s="11">
+        <v>2836100</v>
+      </c>
+      <c r="O15" s="13">
+        <v>0.63</v>
+      </c>
+      <c r="P15" s="14">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A16" s="6">
+        <v>2023</v>
+      </c>
+      <c r="B16" s="11">
+        <v>4</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="12">
+        <v>57</v>
+      </c>
+      <c r="E16" s="12">
+        <v>0.13</v>
+      </c>
+      <c r="F16" s="12">
+        <v>84</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="12">
+        <v>200</v>
+      </c>
+      <c r="I16" s="12">
+        <v>0.03</v>
+      </c>
+      <c r="J16" s="12">
+        <v>33</v>
+      </c>
+      <c r="K16" s="12">
+        <v>150</v>
+      </c>
+      <c r="L16" s="12">
+        <v>306</v>
+      </c>
+      <c r="M16" s="12">
+        <v>149</v>
+      </c>
+      <c r="N16" s="11">
+        <v>5900</v>
+      </c>
+      <c r="O16" s="15">
+        <v>3.5030000000000001</v>
+      </c>
+      <c r="P16" s="15">
+        <v>3.0419999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" s="6">
+        <v>2023</v>
+      </c>
+      <c r="B17" s="11">
+        <v>4</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="12">
+        <v>25</v>
+      </c>
+      <c r="E17" s="12">
+        <v>0.06</v>
+      </c>
+      <c r="F17" s="12">
+        <v>31</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="12">
+        <v>32</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="12">
+        <v>37</v>
+      </c>
+      <c r="K17" s="12">
+        <v>16</v>
+      </c>
+      <c r="L17" s="12">
+        <v>2360</v>
+      </c>
+      <c r="M17" s="12">
+        <v>111</v>
+      </c>
+      <c r="N17" s="11">
+        <v>62368</v>
+      </c>
+      <c r="O17" s="13">
+        <v>0.31</v>
+      </c>
+      <c r="P17" s="15">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18" s="6">
+        <v>2024</v>
+      </c>
+      <c r="B18" s="11">
+        <v>3</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19" s="6">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="11">
+        <v>3</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="12">
+        <v>131</v>
+      </c>
+      <c r="E19" s="12">
+        <v>0.22</v>
+      </c>
+      <c r="F19" s="12">
+        <v>19</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="12">
+        <v>297</v>
+      </c>
+      <c r="I19" s="12">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J19" s="12">
+        <v>178</v>
+      </c>
+      <c r="K19" s="12">
+        <v>368</v>
+      </c>
+      <c r="L19" s="12">
+        <v>5813</v>
+      </c>
+      <c r="M19" s="12">
+        <v>1246</v>
+      </c>
+      <c r="N19" s="11">
+        <v>3809200</v>
+      </c>
+      <c r="O19" s="13">
+        <v>0.41</v>
+      </c>
+      <c r="P19" s="14">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" s="6">
+        <v>2024</v>
+      </c>
+      <c r="B20" s="11">
+        <v>3</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="12">
+        <v>33</v>
+      </c>
+      <c r="E20" s="12">
+        <v>0.08</v>
+      </c>
+      <c r="F20" s="12">
+        <v>39</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="12">
+        <v>33</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="12">
+        <v>44</v>
+      </c>
+      <c r="K20" s="12">
+        <v>21</v>
+      </c>
+      <c r="L20" s="12">
+        <v>1730</v>
+      </c>
+      <c r="M20" s="12">
+        <v>39</v>
+      </c>
+      <c r="N20" s="11">
+        <v>65840</v>
+      </c>
+      <c r="O20" s="13">
+        <v>0.85</v>
+      </c>
+      <c r="P20" s="14">
+        <v>0.19800000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21" s="6">
+        <v>2024</v>
+      </c>
+      <c r="B21" s="11">
+        <v>4</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" s="6">
+        <v>2024</v>
+      </c>
+      <c r="B22" s="11">
+        <v>4</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="12">
+        <v>132</v>
+      </c>
+      <c r="E22" s="12">
+        <v>0.22</v>
+      </c>
+      <c r="F22" s="12">
+        <v>16</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="12">
+        <v>239</v>
+      </c>
+      <c r="I22" s="12">
+        <v>0.06</v>
+      </c>
+      <c r="J22" s="12">
+        <v>175</v>
+      </c>
+      <c r="K22" s="12">
+        <v>126</v>
+      </c>
+      <c r="L22" s="12">
+        <v>3479</v>
+      </c>
+      <c r="M22" s="12">
+        <v>905</v>
+      </c>
+      <c r="N22" s="11">
+        <v>2808750</v>
+      </c>
+      <c r="O22" s="13">
+        <v>0.42</v>
+      </c>
+      <c r="P22" s="14">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" s="6">
         <v>2025</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B23" s="11">
         <v>4</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C23" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D23" s="12">
         <v>40</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E23" s="12">
         <v>0.09</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F23" s="12">
         <v>67</v>
       </c>
-      <c r="G11" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="12">
+      <c r="G23" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="12">
         <v>100</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I23" s="12">
         <v>0.01</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J23" s="12">
         <v>23</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K23" s="12">
         <v>77</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L23" s="12">
         <v>159</v>
       </c>
-      <c r="M11" s="12">
+      <c r="M23" s="12">
         <v>154</v>
       </c>
-      <c r="N11" s="11">
+      <c r="N23" s="11">
         <v>6200</v>
       </c>
-      <c r="O11" s="15">
+      <c r="O23" s="15">
         <v>4.1929999999999996</v>
       </c>
-      <c r="P11" s="15">
+      <c r="P23" s="15">
         <v>2.8679999999999999</v>
       </c>
     </row>
